--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D23E57-46BA-4F14-809A-609270852B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF671D14-2781-4395-A2B8-A9437C1AEE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 19-12-2025'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 29-01-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF671D14-2781-4395-A2B8-A9437C1AEE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEC2D57-3915-47AA-B5D8-8600A8C5F923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 29-01-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 02-02-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEC2D57-3915-47AA-B5D8-8600A8C5F923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B32FD9B-2A67-4985-B243-50C2E804CF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 02-02-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 20-02-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B32FD9B-2A67-4985-B243-50C2E804CF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC28A581-9198-43BC-8AE2-3A844E5CE435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 20-02-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 04-03-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC28A581-9198-43BC-8AE2-3A844E5CE435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007F88D1-A3C0-4351-AE3E-3E654B72BBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 04-03-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 06-03-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007F88D1-A3C0-4351-AE3E-3E654B72BBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FCA631-CC89-4F9E-B970-0E200D7231A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FCA631-CC89-4F9E-B970-0E200D7231A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C7C4DB-04C2-4517-A97C-BD08DA1067B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C7C4DB-04C2-4517-A97C-BD08DA1067B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E845A78A-98FC-49A4-9933-AB9A5FDE9657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 06-03-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 09-03-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E845A78A-98FC-49A4-9933-AB9A5FDE9657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B697CB0-F3D3-42E1-A1D1-BDF4D90050FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B697CB0-F3D3-42E1-A1D1-BDF4D90050FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B65FF9-573A-4BF6-8ABB-A6F5E5ACF10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 09-03-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 11-03-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B65FF9-573A-4BF6-8ABB-A6F5E5ACF10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014A5DBB-424A-4FFC-A0C1-9CCE7250B9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014A5DBB-424A-4FFC-A0C1-9CCE7250B9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DBA69A-7843-45CF-8DE2-B35698B8B72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 11-03-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 20-03-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DBA69A-7843-45CF-8DE2-B35698B8B72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3151CEB5-DE10-4C18-A007-E85E4FE5880A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 20-03-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 25-03-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3151CEB5-DE10-4C18-A007-E85E4FE5880A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCC35F7-B8EE-4D07-8A85-F4C302670E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 25-03-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 08-04-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCC35F7-B8EE-4D07-8A85-F4C302670E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8474695-0417-42B3-8452-B3322A512DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 08-04-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 10-04-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8474695-0417-42B3-8452-B3322A512DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9892FA5-40CE-4130-973A-F63525A27AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9892FA5-40CE-4130-973A-F63525A27AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73DB3A0-BD94-4934-8DFE-84CD2877CD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 10-04-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 14-04-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73DB3A0-BD94-4934-8DFE-84CD2877CD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CED5298-926F-40FD-912F-793AB7F72B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 14-04-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 24-04-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CED5298-926F-40FD-912F-793AB7F72B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2995BD4B-E499-437B-A478-EBF51955D608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2995BD4B-E499-437B-A478-EBF51955D608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805025AB-C508-496E-A98B-B575B986570A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 24-04-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 27-04-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805025AB-C508-496E-A98B-B575B986570A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848DDDCF-AC1B-4A2E-81FE-9A357D746331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 27-04-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 06-05-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848DDDCF-AC1B-4A2E-81FE-9A357D746331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A70D9DE-4140-456A-88E3-8C5842BFB3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 06-05-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 01-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A70D9DE-4140-456A-88E3-8C5842BFB3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B430A56-1D48-424F-932A-550E16CC4079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 01-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 02-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B430A56-1D48-424F-932A-550E16CC4079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD5740C-11B8-43D5-864D-9C78F02C485B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD5740C-11B8-43D5-864D-9C78F02C485B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC270542-FA74-40BC-9F51-B7E49FDC2836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 02-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 05-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF671D14-2781-4395-A2B8-A9437C1AEE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D73C65-69A8-4D33-962A-1D1DD3EBCB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B452E54-073F-4049-9AED-4683D97B8FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE311AD6-403F-435B-9F07-D515E2D97BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE311AD6-403F-435B-9F07-D515E2D97BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F737833B-C504-46B3-AFF9-9F64847FEC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F737833B-C504-46B3-AFF9-9F64847FEC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F49688-E81C-44EB-B903-CF1A39AF8454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 09-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 15-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F49688-E81C-44EB-B903-CF1A39AF8454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61616964-A233-49AE-8756-472B3AC124D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 15-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 22-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61616964-A233-49AE-8756-472B3AC124D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9A2833-3345-455A-B80F-D8E291940156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 22-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 23-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9A2833-3345-455A-B80F-D8E291940156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C96D12-3590-41F2-823D-246D32C9B699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61616964-A233-49AE-8756-472B3AC124D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8365EFE-5FF9-4622-848A-D1859815631D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 22-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 23-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8365EFE-5FF9-4622-848A-D1859815631D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01F43E0-C754-4EB6-A16C-AF1D953D6E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 23-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 25-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01F43E0-C754-4EB6-A16C-AF1D953D6E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4402F31-BEC3-4E67-920A-61A2B03A842A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 25-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 30-06-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4402F31-BEC3-4E67-920A-61A2B03A842A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7B0E9C-F82E-4D71-8391-FFA7A8BEAE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7B0E9C-F82E-4D71-8391-FFA7A8BEAE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66158488-1D21-41F7-B29E-983DD4BC197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 30-06-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 01-07-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66158488-1D21-41F7-B29E-983DD4BC197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB8E232-045A-46E6-8D36-E73816BB1980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 01-07-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 02-07-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66158488-1D21-41F7-B29E-983DD4BC197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CA3706-DF56-413C-8C6E-FC44B4ED89D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 01-07-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 03-07-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB8E232-045A-46E6-8D36-E73816BB1980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA2524-0902-4FE1-94B1-4C5F3B49FC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 02-07-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 03-07-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA2524-0902-4FE1-94B1-4C5F3B49FC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A89DA10-1738-4438-B099-33B7DCB2AB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 03-07-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 09-07-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A89DA10-1738-4438-B099-33B7DCB2AB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6198277-87EF-4840-BDA6-54F54F208AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 09-07-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 19-08-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6198277-87EF-4840-BDA6-54F54F208AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2807E4DB-A342-42BF-A090-C8F61FB171EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 19-08-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 21-08-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2807E4DB-A342-42BF-A090-C8F61FB171EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0794449B-B6CF-4AFA-BE1A-3B3F35FA3E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 21-08-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 27-08-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -647,9 +647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -686,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -703,7 +703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -737,7 +737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -849,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -950,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -964,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>92</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0794449B-B6CF-4AFA-BE1A-3B3F35FA3E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC893607-9AA2-4473-A3D7-D013CD376119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 27-08-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 02-09-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC893607-9AA2-4473-A3D7-D013CD376119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDC8FFD-853F-4785-A128-E86BEBDF1B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 02-09-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 06-09-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDC8FFD-853F-4785-A128-E86BEBDF1B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32CE932-AC33-4B38-97C6-546A63645DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32CE932-AC33-4B38-97C6-546A63645DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F08532-E8C2-4785-9EC9-3E223861B015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 06-09-2026'!$A$1:$F$59</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 07-09-2026'!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E501EBF-1CD8-45FC-BE5F-22144536282C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4C2837-E716-4950-80C4-2FA8EF66C3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 09-09-2026'!$A$1:$G$60</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 09-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -652,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1392,24 +1392,24 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C49" t="s">
         <v>74</v>
       </c>
-      <c r="G49" t="s">
-        <v>13</v>
+      <c r="F49" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
         <v>74</v>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
         <v>74</v>
@@ -1437,21 +1437,21 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
         <v>74</v>
       </c>
       <c r="G52" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
         <v>74</v>
@@ -1462,10 +1462,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s">
         <v>74</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C55" t="s">
         <v>74</v>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
         <v>74</v>
@@ -1504,16 +1504,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C57" t="s">
         <v>74</v>
-      </c>
-      <c r="F57" t="s">
-        <v>13</v>
       </c>
       <c r="G57" t="s">
         <v>10</v>
@@ -1521,43 +1518,60 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
         <v>74</v>
       </c>
-      <c r="E58" t="s">
-        <v>13</v>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C59" t="s">
         <v>74</v>
       </c>
-      <c r="G59" t="s">
-        <v>10</v>
+      <c r="E59" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" t="s">
+        <v>74</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>94</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>95</v>
       </c>
-      <c r="C60" t="s">
-        <v>74</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="C61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61" t="s">
         <v>10</v>
       </c>
     </row>
